--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132065460</v>
       </c>
       <c r="B2" t="n">
-        <v>96387</v>
+        <v>96392</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132065460</v>
       </c>
       <c r="B2" t="n">
-        <v>96392</v>
+        <v>96394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132065460</v>
       </c>
       <c r="B2" t="n">
-        <v>96435</v>
+        <v>96438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132065460</v>
       </c>
       <c r="B2" t="n">
-        <v>96438</v>
+        <v>96446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132065460</v>
       </c>
       <c r="B2" t="n">
-        <v>96446</v>
+        <v>96456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132065460</v>
       </c>
       <c r="B2" t="n">
-        <v>96456</v>
+        <v>96458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132065460</v>
       </c>
       <c r="B2" t="n">
-        <v>96458</v>
+        <v>96459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132065460</v>
       </c>
       <c r="B2" t="n">
-        <v>96459</v>
+        <v>96533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,6 +775,120 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131857782</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92188</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3008</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Timmerticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Amyloporia sinuosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Skallberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>588487</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6572396</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stenkvista</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Hedström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Hedström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59822-2025 artfynd.xlsx
+++ b/artfynd/A 59822-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132065460</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,8 +898,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131857782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>